--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -826,7 +826,7 @@
     <t>0.0000,0.0000,0.0001,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0001,0.0392,0.9983</t>
+    <t>0.0000,0.0001,0.0391,0.9983</t>
   </si>
   <si>
     <t>0.0003,0.0003,0.9118,0.1162</t>
@@ -838,7 +838,7 @@
     <t>0.0000,0.0000,0.0027,0.9999</t>
   </si>
   <si>
-    <t>0.0000,0.0037,0.0322,0.9975</t>
+    <t>0.0000,0.0037,0.0321,0.9975</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0053,0.9998</t>
@@ -859,16 +859,16 @@
     <t>0.0000,0.0000,0.0038,0.9999</t>
   </si>
   <si>
-    <t>0.0001,0.0039,0.1939,0.9309</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0553,0.9964</t>
+    <t>0.0001,0.0039,0.1937,0.9310</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0552,0.9964</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0087,0.9997</t>
   </si>
   <si>
-    <t>0.0005,0.0108,0.8529,0.1517</t>
+    <t>0.0005,0.0108,0.8529,0.1519</t>
   </si>
   <si>
     <t>0.0004,0.0003,0.9479,0.0630</t>
@@ -877,22 +877,22 @@
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0008,0.0743,0.9927</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.1943,0.9638</t>
-  </si>
-  <si>
-    <t>0.0001,0.0074,0.1185,0.9624</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0941,0.9917</t>
+    <t>0.0001,0.0008,0.0742,0.9927</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.1942,0.9638</t>
+  </si>
+  <si>
+    <t>0.0001,0.0074,0.1184,0.9624</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0940,0.9917</t>
   </si>
   <si>
     <t>0.0000,0.0004,0.0866,0.9906</t>
   </si>
   <si>
-    <t>0.0001,0.0003,0.2759,0.9430</t>
+    <t>0.0001,0.0003,0.2758,0.9431</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0011,1.0000</t>
@@ -901,7 +901,7 @@
     <t>0.0000,0.0001,0.0350,0.9976</t>
   </si>
   <si>
-    <t>0.0001,0.0021,0.2145,0.9417</t>
+    <t>0.0001,0.0021,0.2144,0.9418</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0131,0.9994</t>
@@ -919,7 +919,7 @@
     <t>0.0000,0.0000,0.0062,0.9998</t>
   </si>
   <si>
-    <t>0.0001,0.0003,0.1169,0.9878</t>
+    <t>0.0001,0.0003,0.1168,0.9878</t>
   </si>
   <si>
     <t>0.0001,0.0006,0.5121,0.8364</t>
@@ -928,13 +928,13 @@
     <t>0.0000,0.0000,0.0006,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0005,0.0365,0.9982</t>
+    <t>0.0000,0.0005,0.0364,0.9982</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.9783,0.0029</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.0659,0.9847</t>
+    <t>0.0000,0.0000,0.0657,0.9848</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9995,0.0000</t>
@@ -952,10 +952,10 @@
     <t>0.0000,0.0000,0.0129,0.9996</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.0495,0.9974</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0509,0.9977</t>
+    <t>0.0000,0.0000,0.0494,0.9975</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0508,0.9977</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0008,1.0000</t>
@@ -967,7 +967,7 @@
     <t>0.0000,0.0000,0.0009,1.0000</t>
   </si>
   <si>
-    <t>0.0003,0.0006,0.5425,0.7879</t>
+    <t>0.0003,0.0006,0.5424,0.7880</t>
   </si>
 </sst>
 </file>
